--- a/public/PAY_SLIP_Template.xlsx
+++ b/public/PAY_SLIP_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Pay Slips" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
+  <cols>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -467,7 +475,7 @@
         <v>Name:</v>
       </c>
       <c r="C4" t="str">
-        <v>Benedict Olom</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -487,7 +495,7 @@
         <v>Staff No.</v>
       </c>
       <c r="C5" t="str">
-        <v>EMP-001</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -507,7 +515,7 @@
         <v>Period:</v>
       </c>
       <c r="C6" t="str">
-        <v>June 2026</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -527,7 +535,7 @@
         <v>Bank</v>
       </c>
       <c r="C7" t="str">
-        <v>GTBank</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -547,7 +555,7 @@
         <v>Account</v>
       </c>
       <c r="C8" t="str">
-        <v>0123456789</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -567,7 +575,7 @@
         <v>PFA</v>
       </c>
       <c r="C9" t="str">
-        <v>Stanbic IBTC</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -587,7 +595,7 @@
         <v>RSA PIN</v>
       </c>
       <c r="C10" t="str">
-        <v>PEN1000100</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -607,7 +615,7 @@
         <v>TIN</v>
       </c>
       <c r="C11" t="str">
-        <v>TIN-0912</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -627,7 +635,7 @@
         <v>Email</v>
       </c>
       <c r="C12" t="str">
-        <v>olomufeh@gmail.com</v>
+        <v/>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -710,13 +718,13 @@
         <v>BASIC SALARY</v>
       </c>
       <c r="D16" t="str">
-        <v>500000</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>500000</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -730,13 +738,13 @@
         <v>HOUSING ALLOWANCE</v>
       </c>
       <c r="D17" t="str">
-        <v>45000</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>5000</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>50000</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -750,13 +758,13 @@
         <v>TRANSPORT ALLOWANCE</v>
       </c>
       <c r="D18" t="str">
-        <v>30000</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>30000</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -770,13 +778,13 @@
         <v>Gross Pay</v>
       </c>
       <c r="D19" t="str">
-        <v>575000</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>5000</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>580000</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -830,13 +838,13 @@
         <v>PENSION</v>
       </c>
       <c r="D22" t="str">
-        <v>25000</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>25000</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -850,13 +858,13 @@
         <v>PAYE -TAX</v>
       </c>
       <c r="D23" t="str">
-        <v>50000</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>50000</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -870,13 +878,13 @@
         <v>OTHER DEDUCTIONS</v>
       </c>
       <c r="D24" t="str">
-        <v>5000</v>
+        <v/>
       </c>
       <c r="E24" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>5000</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -890,13 +898,13 @@
         <v>Total Deductions</v>
       </c>
       <c r="D25" t="str">
-        <v>80000</v>
+        <v/>
       </c>
       <c r="E25" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>80000</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -933,7 +941,10 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>500000</v>
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1024,7 +1035,7 @@
         <v>Name:</v>
       </c>
       <c r="C32" t="str">
-        <v>Alice Johnson</v>
+        <v/>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1044,7 +1055,7 @@
         <v>Staff No.</v>
       </c>
       <c r="C33" t="str">
-        <v>EMP-002</v>
+        <v/>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1064,7 +1075,7 @@
         <v>Period:</v>
       </c>
       <c r="C34" t="str">
-        <v>June 2026</v>
+        <v/>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -1084,7 +1095,7 @@
         <v>Bank</v>
       </c>
       <c r="C35" t="str">
-        <v>Access Bank</v>
+        <v/>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1104,7 +1115,7 @@
         <v>Account</v>
       </c>
       <c r="C36" t="str">
-        <v>0987654321</v>
+        <v/>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1124,7 +1135,7 @@
         <v>PFA</v>
       </c>
       <c r="C37" t="str">
-        <v>ARM Pensions</v>
+        <v/>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -1144,7 +1155,7 @@
         <v>RSA PIN</v>
       </c>
       <c r="C38" t="str">
-        <v>PEN2000200</v>
+        <v/>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -1164,7 +1175,7 @@
         <v>TIN</v>
       </c>
       <c r="C39" t="str">
-        <v>TIN-8821</v>
+        <v/>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -1184,7 +1195,7 @@
         <v>Email</v>
       </c>
       <c r="C40" t="str">
-        <v>alice@paylogic-test.com</v>
+        <v/>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -1267,13 +1278,13 @@
         <v>BASIC SALARY</v>
       </c>
       <c r="D44" t="str">
-        <v>400000</v>
+        <v/>
       </c>
       <c r="E44" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>400000</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -1287,13 +1298,13 @@
         <v>HOUSING ALLOWANCE</v>
       </c>
       <c r="D45" t="str">
-        <v>40000</v>
+        <v/>
       </c>
       <c r="E45" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F45" t="str">
-        <v>40000</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1307,13 +1318,13 @@
         <v>TRANSPORT ALLOWANCE</v>
       </c>
       <c r="D46" t="str">
-        <v>18000</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>2000</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>20000</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1327,13 +1338,13 @@
         <v>Gross Pay</v>
       </c>
       <c r="D47" t="str">
-        <v>458000</v>
+        <v/>
       </c>
       <c r="E47" t="str">
-        <v>2000</v>
+        <v/>
       </c>
       <c r="F47" t="str">
-        <v>460000</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1387,13 +1398,13 @@
         <v>PENSION</v>
       </c>
       <c r="D50" t="str">
-        <v>20000</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>20000</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1407,13 +1418,13 @@
         <v>PAYE -TAX</v>
       </c>
       <c r="D51" t="str">
-        <v>40000</v>
+        <v/>
       </c>
       <c r="E51" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v>40000</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1427,13 +1438,13 @@
         <v>OTHER DEDUCTIONS</v>
       </c>
       <c r="D52" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E52" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F52" t="str">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1447,13 +1458,13 @@
         <v>Total Deductions</v>
       </c>
       <c r="D53" t="str">
-        <v>60000</v>
+        <v/>
       </c>
       <c r="E53" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>60000</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -1490,17 +1501,15 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F55"/>
   </ignoredErrors>
 </worksheet>
 </file>